--- a/aReport_card/2025_2026/Third_term/JSS1/Third_term_JSS1_Business_Studies.xlsx
+++ b/aReport_card/2025_2026/Third_term/JSS1/Third_term_JSS1_Business_Studies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD668769-108C-4400-ABD1-D583288E02C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BF8D9F-4170-4A78-93FF-6EEC21F25891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,13 +501,14 @@
         <v>34</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>77</v>
+        <f>SUM(C2:E2)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -524,10 +525,11 @@
         <v>28</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>76</v>
+        <f t="shared" ref="F3:F9" si="0">SUM(C3:E3)</f>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -541,13 +543,14 @@
         <v>33</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1">
-        <v>76</v>
+        <f t="shared" si="0"/>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -558,16 +561,17 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1">
         <v>28</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>76</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -581,13 +585,14 @@
         <v>33</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1">
-        <v>76</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -601,13 +606,14 @@
         <v>33</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1">
-        <v>76</v>
+        <f t="shared" si="0"/>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -621,13 +627,14 @@
         <v>34</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1">
-        <v>77</v>
+        <f t="shared" si="0"/>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -644,10 +651,11 @@
         <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1">
-        <v>72</v>
+        <f t="shared" si="0"/>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
